--- a/data/lossofsale_sg_kottayam.xlsx
+++ b/data/lossofsale_sg_kottayam.xlsx
@@ -203,7 +203,7 @@
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="17.55" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
     <col min="5" max="5" width="17.55" customWidth="1"/>
     <col min="6" max="6" width="24.3" customWidth="1"/>
@@ -337,16 +337,16 @@
       </c>
       <c t="inlineStr" r="B4">
         <is>
-          <t xml:space="preserve">11-12-2025</t>
+          <t xml:space="preserve">10-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">asif</t>
+          <t xml:space="preserve">akhil</t>
         </is>
       </c>
       <c r="D4" s="65">
-        <v>8592084968</v>
+        <v>7736286640</v>
       </c>
       <c t="inlineStr" r="E4">
         <is>
@@ -355,7 +355,7 @@
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">Arjun Reji</t>
+          <t xml:space="preserve">DEVADETH R</t>
         </is>
       </c>
       <c t="inlineStr" r="G4">
@@ -365,12 +365,12 @@
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
@@ -380,7 +380,7 @@
       </c>
       <c t="inlineStr" r="K4">
         <is>
-          <t xml:space="preserve">family not like the product</t>
+          <t xml:space="preserve">required item size not hear</t>
         </is>
       </c>
     </row>
@@ -395,20 +395,20 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">bilal</t>
+          <t xml:space="preserve">aswin</t>
         </is>
       </c>
       <c r="D5" s="65">
-        <v>7356639566</v>
+        <v>7012114981</v>
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">21-12-2025</t>
+          <t xml:space="preserve">01-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">Jithinsha R</t>
+          <t xml:space="preserve">DEVADETH R</t>
         </is>
       </c>
       <c t="inlineStr" r="G5">
@@ -418,12 +418,12 @@
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">PRICING</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t xml:space="preserve">RENT TO HIGH</t>
+          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
@@ -433,7 +433,7 @@
       </c>
       <c t="inlineStr" r="K5">
         <is>
-          <t xml:space="preserve">they were looking for a blue premium suit for groom and 7 plain black suit for cousins,But the amount they are expected is too high from here.</t>
+          <t xml:space="preserve">CUTOMER NEED TO CUSTOMIZE</t>
         </is>
       </c>
     </row>
@@ -448,20 +448,20 @@
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">Bibin</t>
+          <t xml:space="preserve">asif</t>
         </is>
       </c>
       <c r="D6" s="65">
-        <v>7907830557</v>
+        <v>8592084968</v>
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">22-01-2026</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
       <c t="inlineStr" r="G6">
@@ -471,12 +471,12 @@
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I6">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
@@ -486,7 +486,7 @@
       </c>
       <c t="inlineStr" r="K6">
         <is>
-          <t xml:space="preserve">THEY ARE OK WITH PREMIUM BLACK SUIT AND BEIGE 3 PC NON PREMIUM,NEEDS TO CONFIRM WITH BRIDE AND REVISIT ASAP</t>
+          <t xml:space="preserve">family not like the product</t>
         </is>
       </c>
     </row>
@@ -496,25 +496,25 @@
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">12-12-2025</t>
+          <t xml:space="preserve">11-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">alimsha</t>
+          <t xml:space="preserve">bilal</t>
         </is>
       </c>
       <c r="D7" s="65">
-        <v>9562165414</v>
+        <v>7356639566</v>
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">22-12-2025</t>
+          <t xml:space="preserve">21-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F7">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Jithinsha R</t>
         </is>
       </c>
       <c t="inlineStr" r="G7">
@@ -524,12 +524,12 @@
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">PRICING</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
         <is>
-          <t xml:space="preserve">SIZE TOO LARGE</t>
+          <t xml:space="preserve">RENT TO HIGH</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
@@ -539,7 +539,7 @@
       </c>
       <c t="inlineStr" r="K7">
         <is>
-          <t xml:space="preserve">customer liked the product ,He only preffer black embo suit 34 but its alredy booked on the same date , next size is big for him and other product are are rejected by him</t>
+          <t xml:space="preserve">they were looking for a blue premium suit for groom and 7 plain black suit for cousins,But the amount they are expected is too high from here.</t>
         </is>
       </c>
     </row>
@@ -549,20 +549,20 @@
       </c>
       <c t="inlineStr" r="B8">
         <is>
-          <t xml:space="preserve">12-12-2025</t>
+          <t xml:space="preserve">11-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">Akku</t>
+          <t xml:space="preserve">Bibin</t>
         </is>
       </c>
       <c r="D8" s="65">
-        <v>8075834843</v>
+        <v>7907830557</v>
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">27-12-2025</t>
+          <t xml:space="preserve">22-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
@@ -577,12 +577,12 @@
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
         <is>
-          <t xml:space="preserve">SIZE TOO SMALL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
@@ -592,7 +592,7 @@
       </c>
       <c t="inlineStr" r="K8">
         <is>
-          <t xml:space="preserve">44 size indowestern not suitable</t>
+          <t xml:space="preserve">THEY ARE OK WITH PREMIUM BLACK SUIT AND BEIGE 3 PC NON PREMIUM,NEEDS TO CONFIRM WITH BRIDE AND REVISIT ASAP</t>
         </is>
       </c>
     </row>
@@ -607,11 +607,11 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">Vishak</t>
+          <t xml:space="preserve">alimsha</t>
         </is>
       </c>
       <c r="D9" s="65">
-        <v>7034766323</v>
+        <v>9562165414</v>
       </c>
       <c t="inlineStr" r="E9">
         <is>
@@ -620,7 +620,7 @@
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G9">
@@ -630,12 +630,12 @@
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">SIZE TOO LARGE</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
@@ -645,7 +645,7 @@
       </c>
       <c t="inlineStr" r="K9">
         <is>
-          <t xml:space="preserve">HE LIKES BLUE SELF PRINT,WILL CHECK WITH FAMILY AND CONFIRM BACK</t>
+          <t xml:space="preserve">customer liked the product ,He only preffer black embo suit 34 but its alredy booked on the same date , next size is big for him and other product are are rejected by him</t>
         </is>
       </c>
     </row>
@@ -655,20 +655,20 @@
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">13-12-2025</t>
+          <t xml:space="preserve">12-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">arjun</t>
+          <t xml:space="preserve">Akku</t>
         </is>
       </c>
       <c r="D10" s="65">
-        <v>9400208644</v>
+        <v>8075834843</v>
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">09-02-2026</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
@@ -683,12 +683,12 @@
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">SIZE NOT SUITABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">SIZE TOO SMALL</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
@@ -698,7 +698,7 @@
       </c>
       <c t="inlineStr" r="K10">
         <is>
-          <t xml:space="preserve">customer is ok with offwhite indo he will discuss with family and revisit again</t>
+          <t xml:space="preserve">44 size indowestern not suitable</t>
         </is>
       </c>
     </row>
@@ -708,25 +708,25 @@
       </c>
       <c t="inlineStr" r="B11">
         <is>
-          <t xml:space="preserve">13-12-2025</t>
+          <t xml:space="preserve">12-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">levin</t>
+          <t xml:space="preserve">Vishak</t>
         </is>
       </c>
       <c r="D11" s="65">
-        <v>9446345585</v>
+        <v>7034766323</v>
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">12-01-2026</t>
+          <t xml:space="preserve">22-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">NANDHU RAJESH</t>
+          <t xml:space="preserve">Aswin Raj M. R</t>
         </is>
       </c>
       <c t="inlineStr" r="G11">
@@ -741,7 +741,7 @@
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
@@ -751,7 +751,7 @@
       </c>
       <c t="inlineStr" r="K11">
         <is>
-          <t xml:space="preserve">They were confirmed premiun IW meroon and black embo,will discuss with family and update by tomorrow</t>
+          <t xml:space="preserve">HE LIKES BLUE SELF PRINT,WILL CHECK WITH FAMILY AND CONFIRM BACK</t>
         </is>
       </c>
     </row>
@@ -761,25 +761,25 @@
       </c>
       <c t="inlineStr" r="B12">
         <is>
-          <t xml:space="preserve">14-12-2025</t>
+          <t xml:space="preserve">13-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">Anson</t>
+          <t xml:space="preserve">arjun</t>
         </is>
       </c>
       <c r="D12" s="65">
-        <v>8157006475</v>
+        <v>9400208644</v>
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">05-01-2026</t>
+          <t xml:space="preserve">09-02-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">Arjun Reji</t>
+          <t xml:space="preserve">Aswin Raj M. R</t>
         </is>
       </c>
       <c t="inlineStr" r="G12">
@@ -794,7 +794,7 @@
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
@@ -804,7 +804,7 @@
       </c>
       <c t="inlineStr" r="K12">
         <is>
-          <t xml:space="preserve">The product ok with customer they will discuss the family and visit again</t>
+          <t xml:space="preserve">customer is ok with offwhite indo he will discuss with family and revisit again</t>
         </is>
       </c>
     </row>
@@ -814,25 +814,25 @@
       </c>
       <c t="inlineStr" r="B13">
         <is>
-          <t xml:space="preserve">14-12-2025</t>
+          <t xml:space="preserve">13-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">joyal</t>
+          <t xml:space="preserve">frederik</t>
         </is>
       </c>
       <c r="D13" s="65">
-        <v>9778238348</v>
+        <v>7034060021</v>
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">08-01-2026</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
         <is>
-          <t xml:space="preserve">NANDHU RAJESH</t>
+          <t xml:space="preserve">DEVADETH R</t>
         </is>
       </c>
       <c t="inlineStr" r="G13">
@@ -842,12 +842,12 @@
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
@@ -857,7 +857,7 @@
       </c>
       <c t="inlineStr" r="K13">
         <is>
-          <t xml:space="preserve">black bulk product 4 qty</t>
+          <t xml:space="preserve">product will be confirm tomorrow</t>
         </is>
       </c>
     </row>
@@ -867,20 +867,20 @@
       </c>
       <c t="inlineStr" r="B14">
         <is>
-          <t xml:space="preserve">15-12-2025</t>
+          <t xml:space="preserve">14-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">shafi</t>
+          <t xml:space="preserve">Anson</t>
         </is>
       </c>
       <c r="D14" s="65">
-        <v>9995786001</v>
+        <v>8157006475</v>
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">11-01-2026</t>
+          <t xml:space="preserve">05-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
@@ -910,7 +910,7 @@
       </c>
       <c t="inlineStr" r="K14">
         <is>
-          <t xml:space="preserve">Price Asking…. And visit again</t>
+          <t xml:space="preserve">The product ok with customer they will discuss the family and visit again</t>
         </is>
       </c>
     </row>
@@ -925,20 +925,20 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">Sachin</t>
+          <t xml:space="preserve">shafi</t>
         </is>
       </c>
       <c r="D15" s="65">
-        <v>8089413584</v>
+        <v>9995786001</v>
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">17-01-2026</t>
+          <t xml:space="preserve">11-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
       <c t="inlineStr" r="G15">
@@ -953,7 +953,7 @@
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
@@ -963,7 +963,7 @@
       </c>
       <c t="inlineStr" r="K15">
         <is>
-          <t xml:space="preserve">visit again</t>
+          <t xml:space="preserve">Price Asking…. And visit again</t>
         </is>
       </c>
     </row>
@@ -978,15 +978,15 @@
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">starlet</t>
+          <t xml:space="preserve">Sachin</t>
         </is>
       </c>
       <c r="D16" s="65">
-        <v>9381340768</v>
+        <v>8089413584</v>
       </c>
       <c t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">07-02-2026</t>
+          <t xml:space="preserve">17-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F16">
@@ -1016,7 +1016,7 @@
       </c>
       <c t="inlineStr" r="K16">
         <is>
-          <t xml:space="preserve">Customer is ok with wine suit he will discuss family and revisit again</t>
+          <t xml:space="preserve">visit again</t>
         </is>
       </c>
     </row>
@@ -1031,20 +1031,20 @@
       </c>
       <c t="inlineStr" r="C17">
         <is>
-          <t xml:space="preserve">JITHU</t>
+          <t xml:space="preserve">starlet</t>
         </is>
       </c>
       <c r="D17" s="65">
-        <v>8848221123</v>
+        <v>9381340768</v>
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">29-01-2026</t>
+          <t xml:space="preserve">07-02-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Aswin Raj M. R</t>
         </is>
       </c>
       <c t="inlineStr" r="G17">
@@ -1069,7 +1069,7 @@
       </c>
       <c t="inlineStr" r="K17">
         <is>
-          <t xml:space="preserve">THEY ARE OK WITH BLUE PREMIUM AND WHITE IW ,CONFIRM WITH BRIDE AND WILL REVISIT</t>
+          <t xml:space="preserve">Customer is ok with wine suit he will discuss family and revisit again</t>
         </is>
       </c>
     </row>
@@ -1079,25 +1079,25 @@
       </c>
       <c t="inlineStr" r="B18">
         <is>
-          <t xml:space="preserve">16-12-2025</t>
+          <t xml:space="preserve">15-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">Robin</t>
+          <t xml:space="preserve">JITHU</t>
         </is>
       </c>
       <c r="D18" s="65">
-        <v>6238812240</v>
+        <v>8848221123</v>
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">14-02-2026</t>
+          <t xml:space="preserve">29-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">Arjun Reji</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G18">
@@ -1112,7 +1112,7 @@
       </c>
       <c t="inlineStr" r="I18">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
@@ -1122,7 +1122,7 @@
       </c>
       <c t="inlineStr" r="K18">
         <is>
-          <t xml:space="preserve">Customer ok with the product.they will discuss and inform tomorrow</t>
+          <t xml:space="preserve">THEY ARE OK WITH BLUE PREMIUM AND WHITE IW ,CONFIRM WITH BRIDE AND WILL REVISIT</t>
         </is>
       </c>
     </row>
@@ -1137,20 +1137,20 @@
       </c>
       <c t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">shiros</t>
+          <t xml:space="preserve">Robin</t>
         </is>
       </c>
       <c r="D19" s="65">
-        <v>9567090630</v>
+        <v>6238812240</v>
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">25-01-2026</t>
+          <t xml:space="preserve">14-02-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">NANDHU RAJESH</t>
+          <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
       <c t="inlineStr" r="G19">
@@ -1160,12 +1160,12 @@
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">SIZE NOT SUITABLE</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t xml:space="preserve">SIZE TOO SMALL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
@@ -1175,7 +1175,7 @@
       </c>
       <c t="inlineStr" r="K19">
         <is>
-          <t xml:space="preserve">They required 44 size IW ,we are showed available 2 models,the customer is in USA,they will confirm once the colour is selected</t>
+          <t xml:space="preserve">Customer ok with the product.they will discuss and inform tomorrow</t>
         </is>
       </c>
     </row>
@@ -1185,25 +1185,25 @@
       </c>
       <c t="inlineStr" r="B20">
         <is>
-          <t xml:space="preserve">17-12-2025</t>
+          <t xml:space="preserve">16-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">Manuel</t>
+          <t xml:space="preserve">joreg</t>
         </is>
       </c>
       <c r="D20" s="65">
-        <v>7411047059</v>
+        <v>7592553007</v>
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">06-01-2026</t>
+          <t xml:space="preserve">28-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">DEVADETH R</t>
         </is>
       </c>
       <c t="inlineStr" r="G20">
@@ -1218,7 +1218,7 @@
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
@@ -1228,7 +1228,7 @@
       </c>
       <c t="inlineStr" r="K20">
         <is>
-          <t xml:space="preserve">customer ok with blue suit he will discuss with family and visit again store</t>
+          <t xml:space="preserve">discuss with family and they will come back in future</t>
         </is>
       </c>
     </row>
@@ -1243,20 +1243,20 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">abhel</t>
+          <t xml:space="preserve">Manuel</t>
         </is>
       </c>
       <c r="D21" s="65">
-        <v>9711815453</v>
+        <v>7411047059</v>
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">12-01-2026</t>
+          <t xml:space="preserve">06-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">Noel Jacob</t>
+          <t xml:space="preserve">Aswin Raj M. R</t>
         </is>
       </c>
       <c t="inlineStr" r="G21">
@@ -1271,7 +1271,7 @@
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
@@ -1281,7 +1281,7 @@
       </c>
       <c t="inlineStr" r="K21">
         <is>
-          <t xml:space="preserve">just enquiry</t>
+          <t xml:space="preserve">customer ok with blue suit he will discuss with family and visit again store</t>
         </is>
       </c>
     </row>
@@ -1291,25 +1291,25 @@
       </c>
       <c t="inlineStr" r="B22">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">17-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">Shon</t>
+          <t xml:space="preserve">mohana krishnan</t>
         </is>
       </c>
       <c r="D22" s="65">
-        <v>9037705576</v>
+        <v>9995805831</v>
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">31-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">DEVADETH R</t>
         </is>
       </c>
       <c t="inlineStr" r="G22">
@@ -1334,7 +1334,7 @@
       </c>
       <c t="inlineStr" r="K22">
         <is>
-          <t xml:space="preserve">Customer tried Gary suit he need to confirm with family function will be January,so he will confirmation with family and revisit</t>
+          <t xml:space="preserve">disscus with family and confirm</t>
         </is>
       </c>
     </row>
@@ -1344,25 +1344,25 @@
       </c>
       <c t="inlineStr" r="B23">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">17-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">prashanth</t>
+          <t xml:space="preserve">abhel</t>
         </is>
       </c>
       <c r="D23" s="65">
-        <v>9946984680</v>
+        <v>9711815453</v>
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">18-12-2025</t>
+          <t xml:space="preserve">12-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">Arjun Reji</t>
+          <t xml:space="preserve">Noel Jacob</t>
         </is>
       </c>
       <c t="inlineStr" r="G23">
@@ -1372,12 +1372,12 @@
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">Product Already Booked</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
@@ -1387,7 +1387,7 @@
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t xml:space="preserve">Product not available</t>
+          <t xml:space="preserve">just enquiry</t>
         </is>
       </c>
     </row>
@@ -1402,20 +1402,20 @@
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">farooq</t>
+          <t xml:space="preserve">Shon</t>
         </is>
       </c>
       <c r="D24" s="65">
-        <v>9645531781</v>
+        <v>9037705576</v>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">04-01-2026</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Aswin Raj M. R</t>
         </is>
       </c>
       <c t="inlineStr" r="G24">
@@ -1425,12 +1425,12 @@
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">Product Already Booked</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
@@ -1440,7 +1440,7 @@
       </c>
       <c t="inlineStr" r="K24">
         <is>
-          <t xml:space="preserve">black indo western. liked the product but that sized product already been  booked on the same date as the customer function date</t>
+          <t xml:space="preserve">Customer tried Gary suit he need to confirm with family function will be January,so he will confirmation with family and revisit</t>
         </is>
       </c>
     </row>
@@ -1455,20 +1455,20 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">Kevin</t>
+          <t xml:space="preserve">prashanth</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>8891387975</v>
+        <v>9946984680</v>
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">17-01-2026</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
       <c t="inlineStr" r="G25">
@@ -1483,7 +1483,7 @@
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+          <t xml:space="preserve">Product Already Booked</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
@@ -1493,7 +1493,7 @@
       </c>
       <c t="inlineStr" r="K25">
         <is>
-          <t xml:space="preserve">He needs 46 size blue velvet indo western or beige indo western,we done have the sizes and modes here for the exact sizes which customer needs</t>
+          <t xml:space="preserve">Product not available</t>
         </is>
       </c>
     </row>
@@ -1503,20 +1503,20 @@
       </c>
       <c t="inlineStr" r="B26">
         <is>
-          <t xml:space="preserve">19-12-2025</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">surya</t>
+          <t xml:space="preserve">farooq</t>
         </is>
       </c>
       <c r="D26" s="65">
-        <v>8281684355</v>
+        <v>9645531781</v>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">30-12-2025</t>
+          <t xml:space="preserve">04-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
@@ -1531,12 +1531,12 @@
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I26">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">Product Already Booked</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
@@ -1546,7 +1546,7 @@
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t xml:space="preserve">customer needs to fix the bride dress ,after fixation he will contact soon as  possible</t>
+          <t xml:space="preserve">black indo western. liked the product but that sized product already been  booked on the same date as the customer function date</t>
         </is>
       </c>
     </row>
@@ -1556,25 +1556,25 @@
       </c>
       <c t="inlineStr" r="B27">
         <is>
-          <t xml:space="preserve">19-12-2025</t>
+          <t xml:space="preserve">18-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">Jithin</t>
+          <t xml:space="preserve">Kevin</t>
         </is>
       </c>
       <c r="D27" s="65">
-        <v>7592971971</v>
+        <v>8891387975</v>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">22-12-2025</t>
+          <t xml:space="preserve">17-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G27">
@@ -1584,12 +1584,12 @@
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
@@ -1599,7 +1599,7 @@
       </c>
       <c t="inlineStr" r="K27">
         <is>
-          <t xml:space="preserve">Customer just visit he dicuss with family and visit again</t>
+          <t xml:space="preserve">He needs 46 size blue velvet indo western or beige indo western,we done have the sizes and modes here for the exact sizes which customer needs</t>
         </is>
       </c>
     </row>
@@ -1614,20 +1614,20 @@
       </c>
       <c t="inlineStr" r="C28">
         <is>
-          <t xml:space="preserve">gopu</t>
+          <t xml:space="preserve">surya</t>
         </is>
       </c>
       <c r="D28" s="65">
-        <v>9745804315</v>
+        <v>8281684355</v>
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t xml:space="preserve">18-01-2026</t>
+          <t xml:space="preserve">30-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
         <is>
-          <t xml:space="preserve">Arjun Reji</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G28">
@@ -1652,7 +1652,7 @@
       </c>
       <c t="inlineStr" r="K28">
         <is>
-          <t xml:space="preserve">The woman's dress has not been confirmed. So they will come together later.</t>
+          <t xml:space="preserve">customer needs to fix the bride dress ,after fixation he will contact soon as  possible</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1662,25 @@
       </c>
       <c t="inlineStr" r="B29">
         <is>
-          <t xml:space="preserve">20-12-2025</t>
+          <t xml:space="preserve">19-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C29">
         <is>
-          <t xml:space="preserve">philemon</t>
+          <t xml:space="preserve">Jithin</t>
         </is>
       </c>
       <c r="D29" s="65">
-        <v>8113834686</v>
+        <v>7592971971</v>
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">28-12-2025</t>
+          <t xml:space="preserve">22-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
         <is>
-          <t xml:space="preserve">Noel Jacob</t>
+          <t xml:space="preserve">Aswin Raj M. R</t>
         </is>
       </c>
       <c t="inlineStr" r="G29">
@@ -1690,12 +1690,12 @@
       </c>
       <c t="inlineStr" r="H29">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I29">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J29">
@@ -1705,7 +1705,7 @@
       </c>
       <c t="inlineStr" r="K29">
         <is>
-          <t xml:space="preserve">They required specific white bengala which is not avilable in our store,it is available in Kochi and perinthalmanna .Will discuss with the  store team to check availability and inform to the customer asap for booking</t>
+          <t xml:space="preserve">Customer just visit he dicuss with family and visit again</t>
         </is>
       </c>
     </row>
@@ -1715,25 +1715,25 @@
       </c>
       <c t="inlineStr" r="B30">
         <is>
-          <t xml:space="preserve">20-12-2025</t>
+          <t xml:space="preserve">19-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C30">
         <is>
-          <t xml:space="preserve">Shaun</t>
+          <t xml:space="preserve">gopu</t>
         </is>
       </c>
       <c r="D30" s="65">
-        <v>8129659152</v>
+        <v>9745804315</v>
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">07-01-2026</t>
+          <t xml:space="preserve">18-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
         <is>
-          <t xml:space="preserve">Jithinsha R</t>
+          <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
       <c t="inlineStr" r="G30">
@@ -1743,12 +1743,12 @@
       </c>
       <c t="inlineStr" r="H30">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I30">
         <is>
-          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J30">
@@ -1758,7 +1758,7 @@
       </c>
       <c t="inlineStr" r="K30">
         <is>
-          <t xml:space="preserve">Customer Needs Sepcific color which is peacock green suites of bulk  8 qty ,we dont have that colour here</t>
+          <t xml:space="preserve">The woman's dress has not been confirmed. So they will come together later.</t>
         </is>
       </c>
     </row>
@@ -1773,20 +1773,20 @@
       </c>
       <c t="inlineStr" r="C31">
         <is>
-          <t xml:space="preserve">ebin</t>
+          <t xml:space="preserve">philemon</t>
         </is>
       </c>
       <c r="D31" s="65">
-        <v>9567225691</v>
+        <v>8113834686</v>
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">10-01-2026</t>
+          <t xml:space="preserve">28-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Noel Jacob</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
@@ -1796,12 +1796,12 @@
       </c>
       <c t="inlineStr" r="H31">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I31">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J31">
@@ -1811,7 +1811,7 @@
       </c>
       <c t="inlineStr" r="K31">
         <is>
-          <t xml:space="preserve">size issue</t>
+          <t xml:space="preserve">They required specific white bengala which is not avilable in our store,it is available in Kochi and perinthalmanna .Will discuss with the  store team to check availability and inform to the customer asap for booking</t>
         </is>
       </c>
     </row>
@@ -1826,20 +1826,20 @@
       </c>
       <c t="inlineStr" r="C32">
         <is>
-          <t xml:space="preserve">sujith</t>
+          <t xml:space="preserve">Shaun</t>
         </is>
       </c>
       <c r="D32" s="65">
-        <v>8113934226</v>
+        <v>8129659152</v>
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">27-12-2025</t>
+          <t xml:space="preserve">07-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Jithinsha R</t>
         </is>
       </c>
       <c t="inlineStr" r="G32">
@@ -1849,12 +1849,12 @@
       </c>
       <c t="inlineStr" r="H32">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I32">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">REQUIRED DESIGN NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J32">
@@ -1864,7 +1864,7 @@
       </c>
       <c t="inlineStr" r="K32">
         <is>
-          <t xml:space="preserve">customer need to fix there colour with bride. he will visit the store tomorrow</t>
+          <t xml:space="preserve">Customer Needs Sepcific color which is peacock green suites of bulk  8 qty ,we dont have that colour here</t>
         </is>
       </c>
     </row>
@@ -1879,20 +1879,20 @@
       </c>
       <c t="inlineStr" r="C33">
         <is>
-          <t xml:space="preserve">basith</t>
+          <t xml:space="preserve">ebin</t>
         </is>
       </c>
       <c r="D33" s="65">
-        <v>7902662404</v>
+        <v>9567225691</v>
       </c>
       <c t="inlineStr" r="E33">
         <is>
-          <t xml:space="preserve">11-01-2026</t>
+          <t xml:space="preserve">10-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F33">
         <is>
-          <t xml:space="preserve">Noel Jacob</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G33">
@@ -1902,12 +1902,12 @@
       </c>
       <c t="inlineStr" r="H33">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I33">
         <is>
-          <t xml:space="preserve">Product Already Booked</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J33">
@@ -1917,7 +1917,7 @@
       </c>
       <c t="inlineStr" r="K33">
         <is>
-          <t xml:space="preserve">they needs 34 green texture ,but its also booked ,will checked with other stores and inform the customer for availability</t>
+          <t xml:space="preserve">size issue</t>
         </is>
       </c>
     </row>
@@ -1927,25 +1927,25 @@
       </c>
       <c t="inlineStr" r="B34">
         <is>
-          <t xml:space="preserve">21-12-2025</t>
+          <t xml:space="preserve">20-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C34">
         <is>
-          <t xml:space="preserve">bibin</t>
+          <t xml:space="preserve">sujith</t>
         </is>
       </c>
       <c r="D34" s="65">
-        <v>7994681733</v>
+        <v>8113934226</v>
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">15-01-2026</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
         <is>
-          <t xml:space="preserve">Noel Jacob</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G34">
@@ -1960,7 +1960,7 @@
       </c>
       <c t="inlineStr" r="I34">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
         </is>
       </c>
       <c t="inlineStr" r="J34">
@@ -1970,7 +1970,7 @@
       </c>
       <c t="inlineStr" r="K34">
         <is>
-          <t xml:space="preserve">want kurta work model not in our store currently</t>
+          <t xml:space="preserve">customer need to fix there colour with bride. he will visit the store tomorrow</t>
         </is>
       </c>
     </row>
@@ -1980,20 +1980,20 @@
       </c>
       <c t="inlineStr" r="B35">
         <is>
-          <t xml:space="preserve">21-12-2025</t>
+          <t xml:space="preserve">20-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C35">
         <is>
-          <t xml:space="preserve">james</t>
+          <t xml:space="preserve">basith</t>
         </is>
       </c>
       <c r="D35" s="65">
-        <v>9778431334</v>
+        <v>7902662404</v>
       </c>
       <c t="inlineStr" r="E35">
         <is>
-          <t xml:space="preserve">03-01-2026</t>
+          <t xml:space="preserve">11-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F35">
@@ -2008,12 +2008,12 @@
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I35">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">Product Already Booked</t>
         </is>
       </c>
       <c t="inlineStr" r="J35">
@@ -2023,7 +2023,7 @@
       </c>
       <c t="inlineStr" r="K35">
         <is>
-          <t xml:space="preserve">date issue want charcoal gery colour</t>
+          <t xml:space="preserve">they needs 34 green texture ,but its also booked ,will checked with other stores and inform the customer for availability</t>
         </is>
       </c>
     </row>
@@ -2042,16 +2042,16 @@
         </is>
       </c>
       <c r="D36" s="65">
-        <v>9048044474</v>
+        <v>7994681733</v>
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">28-12-2025</t>
+          <t xml:space="preserve">15-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Noel Jacob</t>
         </is>
       </c>
       <c t="inlineStr" r="G36">
@@ -2061,12 +2061,12 @@
       </c>
       <c t="inlineStr" r="H36">
         <is>
-          <t xml:space="preserve">PRODUCT</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I36">
         <is>
-          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J36">
@@ -2076,7 +2076,7 @@
       </c>
       <c t="inlineStr" r="K36">
         <is>
-          <t xml:space="preserve">required model is not available</t>
+          <t xml:space="preserve">want kurta work model not in our store currently</t>
         </is>
       </c>
     </row>
@@ -2086,16 +2086,16 @@
       </c>
       <c t="inlineStr" r="B37">
         <is>
-          <t xml:space="preserve">22-12-2025</t>
+          <t xml:space="preserve">21-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C37">
         <is>
-          <t xml:space="preserve">ivin</t>
+          <t xml:space="preserve">james</t>
         </is>
       </c>
       <c r="D37" s="65">
-        <v>9020244484</v>
+        <v>9778431334</v>
       </c>
       <c t="inlineStr" r="E37">
         <is>
@@ -2114,12 +2114,12 @@
       </c>
       <c t="inlineStr" r="H37">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I37">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J37">
@@ -2129,7 +2129,7 @@
       </c>
       <c t="inlineStr" r="K37">
         <is>
-          <t xml:space="preserve">They are looking for a suit,we are showed multiple items ,he will confirm with family and will revisit again</t>
+          <t xml:space="preserve">date issue want charcoal gery colour</t>
         </is>
       </c>
     </row>
@@ -2139,16 +2139,16 @@
       </c>
       <c t="inlineStr" r="B38">
         <is>
-          <t xml:space="preserve">22-12-2025</t>
+          <t xml:space="preserve">21-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C38">
         <is>
-          <t xml:space="preserve">saji</t>
+          <t xml:space="preserve">bibin</t>
         </is>
       </c>
       <c r="D38" s="65">
-        <v>9544577340</v>
+        <v>9048044474</v>
       </c>
       <c t="inlineStr" r="E38">
         <is>
@@ -2157,7 +2157,7 @@
       </c>
       <c t="inlineStr" r="F38">
         <is>
-          <t xml:space="preserve">Noel Jacob</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G38">
@@ -2167,12 +2167,12 @@
       </c>
       <c t="inlineStr" r="H38">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
       <c t="inlineStr" r="I38">
         <is>
-          <t xml:space="preserve">Enquiry for Relative/Friend</t>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
         </is>
       </c>
       <c t="inlineStr" r="J38">
@@ -2182,7 +2182,7 @@
       </c>
       <c t="inlineStr" r="K38">
         <is>
-          <t xml:space="preserve">they need green colour non premium 3peace suit  different sizes. and they want opinion from cousins revist again</t>
+          <t xml:space="preserve">required model is not available</t>
         </is>
       </c>
     </row>
@@ -2197,20 +2197,20 @@
       </c>
       <c t="inlineStr" r="C39">
         <is>
-          <t xml:space="preserve">febin</t>
+          <t xml:space="preserve">ivin</t>
         </is>
       </c>
       <c r="D39" s="65">
-        <v>9207420831</v>
+        <v>9020244484</v>
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">12-01-2026</t>
+          <t xml:space="preserve">03-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
         <is>
-          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+          <t xml:space="preserve">Noel Jacob</t>
         </is>
       </c>
       <c t="inlineStr" r="G39">
@@ -2220,12 +2220,12 @@
       </c>
       <c t="inlineStr" r="H39">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I39">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J39">
@@ -2235,7 +2235,7 @@
       </c>
       <c t="inlineStr" r="K39">
         <is>
-          <t xml:space="preserve">they have checked the products which is suits for him,will revisit with bride in upcoming days</t>
+          <t xml:space="preserve">They are looking for a suit,we are showed multiple items ,he will confirm with family and will revisit again</t>
         </is>
       </c>
     </row>
@@ -2250,15 +2250,15 @@
       </c>
       <c t="inlineStr" r="C40">
         <is>
-          <t xml:space="preserve">jims</t>
+          <t xml:space="preserve">saji</t>
         </is>
       </c>
       <c r="D40" s="65">
-        <v>9731146756</v>
+        <v>9544577340</v>
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">15-01-2026</t>
+          <t xml:space="preserve">28-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
@@ -2278,7 +2278,7 @@
       </c>
       <c t="inlineStr" r="I40">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+          <t xml:space="preserve">Enquiry for Relative/Friend</t>
         </is>
       </c>
       <c t="inlineStr" r="J40">
@@ -2288,7 +2288,7 @@
       </c>
       <c t="inlineStr" r="K40">
         <is>
-          <t xml:space="preserve">just enquiry revist on 3 days</t>
+          <t xml:space="preserve">they need green colour non premium 3peace suit  different sizes. and they want opinion from cousins revist again</t>
         </is>
       </c>
     </row>
@@ -2303,20 +2303,20 @@
       </c>
       <c t="inlineStr" r="C41">
         <is>
-          <t xml:space="preserve">Hari</t>
+          <t xml:space="preserve">febin</t>
         </is>
       </c>
       <c r="D41" s="65">
-        <v>9747511995</v>
+        <v>9207420831</v>
       </c>
       <c t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">29-12-2025</t>
+          <t xml:space="preserve">12-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F41">
         <is>
-          <t xml:space="preserve">Jithinsha R</t>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
         </is>
       </c>
       <c t="inlineStr" r="G41">
@@ -2341,7 +2341,7 @@
       </c>
       <c t="inlineStr" r="K41">
         <is>
-          <t xml:space="preserve">Customer ok with Navy blue and Peacock blue bengala,He needs a suires for wedding also.he will revisit the store by tomorrw for booking for both items</t>
+          <t xml:space="preserve">they have checked the products which is suits for him,will revisit with bride in upcoming days</t>
         </is>
       </c>
     </row>
@@ -2351,25 +2351,25 @@
       </c>
       <c t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">23-12-2025</t>
+          <t xml:space="preserve">22-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C42">
         <is>
-          <t xml:space="preserve">Alvin</t>
+          <t xml:space="preserve">jims</t>
         </is>
       </c>
       <c r="D42" s="65">
-        <v>9495564724</v>
+        <v>9731146756</v>
       </c>
       <c t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">27-12-2025</t>
+          <t xml:space="preserve">15-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F42">
         <is>
-          <t xml:space="preserve">Aswin Raj M. R</t>
+          <t xml:space="preserve">Noel Jacob</t>
         </is>
       </c>
       <c t="inlineStr" r="G42">
@@ -2394,7 +2394,7 @@
       </c>
       <c t="inlineStr" r="K42">
         <is>
-          <t xml:space="preserve">want black embro but dates are not available</t>
+          <t xml:space="preserve">just enquiry revist on 3 days</t>
         </is>
       </c>
     </row>
@@ -2404,25 +2404,25 @@
       </c>
       <c t="inlineStr" r="B43">
         <is>
-          <t xml:space="preserve">23-12-2025</t>
+          <t xml:space="preserve">22-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C43">
         <is>
-          <t xml:space="preserve">sachin</t>
+          <t xml:space="preserve">Hari</t>
         </is>
       </c>
       <c r="D43" s="65">
-        <v>9495574128</v>
+        <v>9747511995</v>
       </c>
       <c t="inlineStr" r="E43">
         <is>
-          <t xml:space="preserve">27-12-2025</t>
+          <t xml:space="preserve">29-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F43">
         <is>
-          <t xml:space="preserve">Arjun Reji</t>
+          <t xml:space="preserve">Jithinsha R</t>
         </is>
       </c>
       <c t="inlineStr" r="G43">
@@ -2432,12 +2432,12 @@
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+          <t xml:space="preserve">ENQUIRY</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
@@ -2447,7 +2447,7 @@
       </c>
       <c t="inlineStr" r="K43">
         <is>
-          <t xml:space="preserve">He was okey with the product but family was disapprovel</t>
+          <t xml:space="preserve">Customer ok with Navy blue and Peacock blue bengala,He needs a suires for wedding also.he will revisit the store by tomorrw for booking for both items</t>
         </is>
       </c>
     </row>
@@ -2462,15 +2462,15 @@
       </c>
       <c t="inlineStr" r="C44">
         <is>
-          <t xml:space="preserve">Ashok</t>
+          <t xml:space="preserve">Alvin</t>
         </is>
       </c>
       <c r="D44" s="65">
-        <v>8714298728</v>
+        <v>9495564724</v>
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t xml:space="preserve">07-01-2026</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
@@ -2500,7 +2500,7 @@
       </c>
       <c t="inlineStr" r="K44">
         <is>
-          <t xml:space="preserve">Customer is ok with biege suit he discuss with bride and family and visit again</t>
+          <t xml:space="preserve">want black embro but dates are not available</t>
         </is>
       </c>
     </row>
@@ -2510,20 +2510,20 @@
       </c>
       <c t="inlineStr" r="B45">
         <is>
-          <t xml:space="preserve">24-12-2025</t>
+          <t xml:space="preserve">23-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C45">
         <is>
-          <t xml:space="preserve">rasal</t>
+          <t xml:space="preserve">sachin</t>
         </is>
       </c>
       <c r="D45" s="65">
-        <v>9072226848</v>
+        <v>9495574128</v>
       </c>
       <c t="inlineStr" r="E45">
         <is>
-          <t xml:space="preserve">11-01-2026</t>
+          <t xml:space="preserve">27-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="F45">
@@ -2538,12 +2538,12 @@
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">ENQUIRY</t>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
         </is>
       </c>
       <c t="inlineStr" r="J45">
@@ -2553,7 +2553,7 @@
       </c>
       <c t="inlineStr" r="K45">
         <is>
-          <t xml:space="preserve">Enquiry and price details</t>
+          <t xml:space="preserve">He was okey with the product but family was disapprovel</t>
         </is>
       </c>
     </row>
@@ -2563,20 +2563,20 @@
       </c>
       <c t="inlineStr" r="B46">
         <is>
-          <t xml:space="preserve">24-12-2025</t>
+          <t xml:space="preserve">23-12-2025</t>
         </is>
       </c>
       <c t="inlineStr" r="C46">
         <is>
-          <t xml:space="preserve">Deepak</t>
+          <t xml:space="preserve">Ashok</t>
         </is>
       </c>
       <c r="D46" s="65">
-        <v>8848355981</v>
+        <v>8714298728</v>
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">28-12-2025</t>
+          <t xml:space="preserve">07-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
@@ -2596,7 +2596,7 @@
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
@@ -2606,7 +2606,7 @@
       </c>
       <c t="inlineStr" r="K46">
         <is>
-          <t xml:space="preserve">just visit</t>
+          <t xml:space="preserve">Customer is ok with biege suit he discuss with bride and family and visit again</t>
         </is>
       </c>
     </row>
@@ -2621,20 +2621,20 @@
       </c>
       <c t="inlineStr" r="C47">
         <is>
-          <t xml:space="preserve">johnson</t>
+          <t xml:space="preserve">rasal</t>
         </is>
       </c>
       <c r="D47" s="65">
-        <v>8891512403</v>
+        <v>9072226848</v>
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">06-01-2026</t>
+          <t xml:space="preserve">11-01-2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
         <is>
-          <t xml:space="preserve">Noel Jacob</t>
+          <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
       <c t="inlineStr" r="G47">
@@ -2659,7 +2659,7 @@
       </c>
       <c t="inlineStr" r="K47">
         <is>
-          <t xml:space="preserve">want black colour short work model  and that product already booked for another custmor</t>
+          <t xml:space="preserve">Enquiry and price details</t>
         </is>
       </c>
     </row>
@@ -2674,45 +2674,1476 @@
       </c>
       <c t="inlineStr" r="C48">
         <is>
+          <t xml:space="preserve">Deepak</t>
+        </is>
+      </c>
+      <c r="D48" s="65">
+        <v>8848355981</v>
+      </c>
+      <c t="inlineStr" r="E48">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F48">
+        <is>
+          <t xml:space="preserve">Aswin Raj M. R</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G48">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H48">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I48">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J48">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K48">
+        <is>
+          <t xml:space="preserve">just visit</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="65">
+        <v>47</v>
+      </c>
+      <c t="inlineStr" r="B49">
+        <is>
+          <t xml:space="preserve">24-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C49">
+        <is>
+          <t xml:space="preserve">johnson</t>
+        </is>
+      </c>
+      <c r="D49" s="65">
+        <v>8891512403</v>
+      </c>
+      <c t="inlineStr" r="E49">
+        <is>
+          <t xml:space="preserve">06-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F49">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G49">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H49">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I49">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J49">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K49">
+        <is>
+          <t xml:space="preserve">want black colour short work model  and that product already booked for another custmor</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="65">
+        <v>48</v>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">24-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C50">
+        <is>
           <t xml:space="preserve">philip</t>
         </is>
       </c>
-      <c r="D48" s="65">
+      <c r="D50" s="65">
         <v>7736254684</v>
       </c>
-      <c t="inlineStr" r="E48">
+      <c t="inlineStr" r="E50">
         <is>
           <t xml:space="preserve">08-01-2026</t>
         </is>
       </c>
-      <c t="inlineStr" r="F48">
+      <c t="inlineStr" r="F50">
         <is>
           <t xml:space="preserve">Arjun Reji</t>
         </is>
       </c>
-      <c t="inlineStr" r="G48">
-        <is>
-          <t xml:space="preserve">Loss</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="H48">
+      <c t="inlineStr" r="G50">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H50">
         <is>
           <t xml:space="preserve">PRODUCT</t>
         </is>
       </c>
-      <c t="inlineStr" r="I48">
+      <c t="inlineStr" r="I50">
         <is>
           <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
         </is>
       </c>
-      <c t="inlineStr" r="J48">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="K48">
+      <c t="inlineStr" r="J50">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K50">
         <is>
           <t xml:space="preserve">He was ok with the product.but the product not for available at the date</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>49</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">kevin</t>
+        </is>
+      </c>
+      <c r="D51" s="65">
+        <v>8939813777</v>
+      </c>
+      <c t="inlineStr" r="E51">
+        <is>
+          <t xml:space="preserve">31-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F51">
+        <is>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G51">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H51">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I51">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J51">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K51">
+        <is>
+          <t xml:space="preserve">groom currently not available.family came and enquired the product details. they will purchase the product when the groom came</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>50</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">asher</t>
+        </is>
+      </c>
+      <c r="D52" s="65">
+        <v>7970573301</v>
+      </c>
+      <c t="inlineStr" r="E52">
+        <is>
+          <t xml:space="preserve">21-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F52">
+        <is>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G52">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H52">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I52">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J52">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K52">
+        <is>
+          <t xml:space="preserve">they want bulk product for 7 . they will inform they were oke with shop currently available product</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>51</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">thomas</t>
+        </is>
+      </c>
+      <c r="D53" s="65">
+        <v>9947184401</v>
+      </c>
+      <c t="inlineStr" r="E53">
+        <is>
+          <t xml:space="preserve">03-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F53">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G53">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H53">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I53">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J53">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K53">
+        <is>
+          <t xml:space="preserve">want bangala  very small size</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>52</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">jaslin</t>
+        </is>
+      </c>
+      <c r="D54" s="65">
+        <v>8075369885</v>
+      </c>
+      <c t="inlineStr" r="E54">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F54">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G54">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H54">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I54">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J54">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K54">
+        <is>
+          <t xml:space="preserve">He want black suit 5 qnty but the product no for available for the date</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>53</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">Nandhu</t>
+        </is>
+      </c>
+      <c r="D55" s="65">
+        <v>6235769239</v>
+      </c>
+      <c t="inlineStr" r="E55">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F55">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G55">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H55">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I55">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J55">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K55">
+        <is>
+          <t xml:space="preserve">He was oke with that product but the bride disapproved</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>54</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">Jomal</t>
+        </is>
+      </c>
+      <c r="D56" s="65">
+        <v>9207007764</v>
+      </c>
+      <c t="inlineStr" r="E56">
+        <is>
+          <t xml:space="preserve">07-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F56">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G56">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H56">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I56">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J56">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K56">
+        <is>
+          <t xml:space="preserve">JUST VISIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>55</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">26-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">sujith</t>
+        </is>
+      </c>
+      <c r="D57" s="65">
+        <v>9037294754</v>
+      </c>
+      <c t="inlineStr" r="E57">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F57">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G57">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H57">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I57">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J57">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K57">
+        <is>
+          <t xml:space="preserve">looking product not in our store</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>56</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">bony</t>
+        </is>
+      </c>
+      <c r="D58" s="65">
+        <v>8590452699</v>
+      </c>
+      <c t="inlineStr" r="E58">
+        <is>
+          <t xml:space="preserve">04-02-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F58">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G58">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H58">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I58">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J58">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K58">
+        <is>
+          <t xml:space="preserve">want navy blue bangala but the size is currently not available in our store</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>57</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">Lijo</t>
+        </is>
+      </c>
+      <c r="D59" s="65">
+        <v>7012452154</v>
+      </c>
+      <c t="inlineStr" r="E59">
+        <is>
+          <t xml:space="preserve">02-05-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F59">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G59">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H59">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I59">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J59">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K59">
+        <is>
+          <t xml:space="preserve">They was oke with product.confirmation soon . the function date was may 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>58</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">sachin</t>
+        </is>
+      </c>
+      <c r="D60" s="65">
+        <v>9087829839</v>
+      </c>
+      <c t="inlineStr" r="E60">
+        <is>
+          <t xml:space="preserve">12-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F60">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G60">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H60">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I60">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J60">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K60">
+        <is>
+          <t xml:space="preserve">just enquiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="65">
+        <v>59</v>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">febon</t>
+        </is>
+      </c>
+      <c r="D61" s="65">
+        <v>7012386605</v>
+      </c>
+      <c t="inlineStr" r="E61">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F61">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G61">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H61">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I61">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J61">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K61">
+        <is>
+          <t xml:space="preserve">confirmation on tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="65">
+        <v>60</v>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">aroger</t>
+        </is>
+      </c>
+      <c r="D62" s="65">
+        <v>8714727974</v>
+      </c>
+      <c t="inlineStr" r="E62">
+        <is>
+          <t xml:space="preserve">18-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F62">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G62">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H62">
+        <is>
+          <t xml:space="preserve">PRICING</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I62">
+        <is>
+          <t xml:space="preserve">RENT TO HIGH</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J62">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K62">
+        <is>
+          <t xml:space="preserve">Price to high . he will visit again</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="65">
+        <v>61</v>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">elvin</t>
+        </is>
+      </c>
+      <c r="D63" s="65">
+        <v>9567322044</v>
+      </c>
+      <c t="inlineStr" r="E63">
+        <is>
+          <t xml:space="preserve">09-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F63">
+        <is>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G63">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H63">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I63">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J63">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K63">
+        <is>
+          <t xml:space="preserve">they looked for a particular product. but that's not available in store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="65">
+        <v>62</v>
+      </c>
+      <c t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C64">
+        <is>
+          <t xml:space="preserve">Ajeesh</t>
+        </is>
+      </c>
+      <c r="D64" s="65">
+        <v>7306648344</v>
+      </c>
+      <c t="inlineStr" r="E64">
+        <is>
+          <t xml:space="preserve">07-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F64">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G64">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H64">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I64">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J64">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K64">
+        <is>
+          <t xml:space="preserve">customer is not satisfied with our product. need improvement in our products</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="65">
+        <v>63</v>
+      </c>
+      <c t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C65">
+        <is>
+          <t xml:space="preserve">jelson</t>
+        </is>
+      </c>
+      <c r="D65" s="65">
+        <v>7012112295</v>
+      </c>
+      <c t="inlineStr" r="E65">
+        <is>
+          <t xml:space="preserve">03-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F65">
+        <is>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G65">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H65">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I65">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J65">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K65">
+        <is>
+          <t xml:space="preserve">groom is oke with bengala navy blue but need to confirm with bride</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="65">
+        <v>64</v>
+      </c>
+      <c t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">27-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">lijo</t>
+        </is>
+      </c>
+      <c r="D66" s="65">
+        <v>8089245819</v>
+      </c>
+      <c t="inlineStr" r="E66">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F66">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G66">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H66">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I66">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT BRIDE/FAMILY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J66">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K66">
+        <is>
+          <t xml:space="preserve">revist again</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="65">
+        <v>65</v>
+      </c>
+      <c t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">Antony</t>
+        </is>
+      </c>
+      <c r="D67" s="65">
+        <v>8157032390</v>
+      </c>
+      <c t="inlineStr" r="E67">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F67">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G67">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H67">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I67">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J67">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K67">
+        <is>
+          <t xml:space="preserve">product not available for trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65">
+        <v>66</v>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">santhosh kumar</t>
+        </is>
+      </c>
+      <c r="D68" s="65">
+        <v>9605574785</v>
+      </c>
+      <c t="inlineStr" r="E68">
+        <is>
+          <t xml:space="preserve">03-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F68">
+        <is>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G68">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H68">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I68">
+        <is>
+          <t xml:space="preserve">REQUIRED MODEL NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J68">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K68">
+        <is>
+          <t xml:space="preserve">customer just to enquiry about product and he taken few photos of shop products after discussion with his styler.hw will contact back to the store .if the styler agrrees</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>67</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">alex</t>
+        </is>
+      </c>
+      <c r="D69" s="65">
+        <v>9895824481</v>
+      </c>
+      <c t="inlineStr" r="E69">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F69">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G69">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H69">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I69">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J69">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K69">
+        <is>
+          <t xml:space="preserve">BRIDE NOT SATISFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>68</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">jithin</t>
+        </is>
+      </c>
+      <c r="D70" s="65">
+        <v>9947402146</v>
+      </c>
+      <c t="inlineStr" r="E70">
+        <is>
+          <t xml:space="preserve">08-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F70">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G70">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H70">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I70">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J70">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K70">
+        <is>
+          <t xml:space="preserve">want off white colur size not available in our store</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>69</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">28-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">abin</t>
+        </is>
+      </c>
+      <c r="D71" s="65">
+        <v>9074998436</v>
+      </c>
+      <c t="inlineStr" r="E71">
+        <is>
+          <t xml:space="preserve">31-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F71">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G71">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H71">
+        <is>
+          <t xml:space="preserve">CUSTOMER INTERNAL ISSUES</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I71">
+        <is>
+          <t xml:space="preserve">FAMILY DISAPPROVEL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J71">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K71">
+        <is>
+          <t xml:space="preserve">He was ok with the product. confirmation Tomorrow morning</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>70</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">sethu</t>
+        </is>
+      </c>
+      <c r="D72" s="65">
+        <v>8848234849</v>
+      </c>
+      <c t="inlineStr" r="E72">
+        <is>
+          <t xml:space="preserve">26-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F72">
+        <is>
+          <t xml:space="preserve">ABHIJITH KUMAR P A</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G72">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H72">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I72">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J72">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K72">
+        <is>
+          <t xml:space="preserve">groom is physically unavailable currently. after he became available he will visit the store</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>71</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">george</t>
+        </is>
+      </c>
+      <c r="D73" s="65">
+        <v>7902395172</v>
+      </c>
+      <c t="inlineStr" r="E73">
+        <is>
+          <t xml:space="preserve">03-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F73">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G73">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H73">
+        <is>
+          <t xml:space="preserve">ENQUIRY</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I73">
+        <is>
+          <t xml:space="preserve">ENQUIRY WITHOUT TRIAL</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J73">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K73">
+        <is>
+          <t xml:space="preserve">enquiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>72</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">TIBIN</t>
+        </is>
+      </c>
+      <c r="D74" s="65">
+        <v>8891696680</v>
+      </c>
+      <c t="inlineStr" r="E74">
+        <is>
+          <t xml:space="preserve">05-01-2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F74">
+        <is>
+          <t xml:space="preserve">Noel Jacob</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G74">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H74">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I74">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J74">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K74">
+        <is>
+          <t xml:space="preserve">They required plain black suit for groom men,the size which he tried are not available on that date</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>73</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">29-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">joli</t>
+        </is>
+      </c>
+      <c r="D75" s="65">
+        <v>8547892605</v>
+      </c>
+      <c t="inlineStr" r="E75">
+        <is>
+          <t xml:space="preserve">31-12-2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F75">
+        <is>
+          <t xml:space="preserve">Arjun Reji</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="G75">
+        <is>
+          <t xml:space="preserve">Loss</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H75">
+        <is>
+          <t xml:space="preserve">PRODUCT</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I75">
+        <is>
+          <t xml:space="preserve">PRODUCT NOT AVAILABLE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J75">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K75">
+        <is>
+          <t xml:space="preserve">Trouser not available for the function date</t>
         </is>
       </c>
     </row>
